--- a/reports/historical_reports_ExtendedKalmanTest.xlsx
+++ b/reports/historical_reports_ExtendedKalmanTest.xlsx
@@ -20,6 +20,7 @@
     <sheet name="20260711-180732" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="20260713-142056" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="20260713-175837" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="20260715-192458" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2614,7 +2615,6 @@
           <t>Annualised return (CAGR)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -2632,7 +2632,6 @@
           <t>Annual volatility (Log Return)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -2650,7 +2649,6 @@
           <t>Sharpe ratio (log returns)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -2668,7 +2666,6 @@
           <t>Calmar ratio</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -2686,7 +2683,6 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -2766,6 +2762,514 @@
       </c>
       <c r="B48" t="n">
         <v>55.26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ExtendedKalmanTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.q_acc</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1e-10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>param.k_exit</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>param.min_hold</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>param.cost_mult</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>param.commission</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>param.drag_m</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>param.c_d_window</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>param.trend_bias</t>
+        </is>
+      </c>
+      <c r="B20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2025-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.092821</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-0.092821</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.285324</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.286215</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-0.408847</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-0.543941</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>-0.6200020000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.295204</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>-0.314428</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.018558</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.957053</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>-0.00382</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.498563</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>42.486007</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>53.53</v>
       </c>
     </row>
   </sheetData>
